--- a/raw-xlsx/116Bidhannagar_2026_Form20.xlsx
+++ b/raw-xlsx/116Bidhannagar_2026_Form20.xlsx
@@ -463,7 +463,7 @@
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M202" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M203" s="2" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M204" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M208" s="2" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M209" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M210" s="2" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M213" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M214" s="2" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M216" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M217" s="2" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M218" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M219" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M225" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M227" s="2" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M228" s="2" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M229" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M230" s="2" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M231" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M232" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M233" s="2" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M234" s="2" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M235" s="2" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M236" s="2" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M237" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M238" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M239" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M240" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M241" s="2" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M242" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M243" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M244" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M246" s="2" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M247" s="2" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M248" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M249" s="2" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M250" s="2" t="inlineStr">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M251" s="2" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M252" s="2" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M256" s="2" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M259" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M264" s="2" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M265" s="2" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M266" s="2" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M269" s="2" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M270" s="2" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M271" s="2" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M272" s="2" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M273" s="2" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M274" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M275" s="2" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M277" s="2" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M278" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M279" s="2" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M280" s="2" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M281" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M282" s="2" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M283" s="2" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M284" s="2" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M285" s="2" t="inlineStr">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>SOUTH DUM DUM</t>
+          <t>BIDHANNAGAR MUNICIPAL</t>
         </is>
       </c>
       <c r="M286" s="2" t="inlineStr">
